--- a/ცელერისი TBC.xlsx
+++ b/ცელერისი TBC.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676B690-82D1-427A-9E5E-C62F03D7274F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B487F0-A3AC-43CA-A887-074CB03628B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GE98TB7581136070100003-GEL" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GE98TB7581136070100003-GEL'!$A$1:$Z$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GE98TB7581136070100003-GEL'!$A$1:$Z$16</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -94,15 +94,39 @@
     <t>Transaction ID</t>
   </si>
   <si>
+    <t>ყვითელი ნაკრები ნაკრების საკომისიო, ივლისი, 2026</t>
+  </si>
+  <si>
+    <t>დებიტორები - მისაღები ნაკრებების საკომისიო, TBCBGE22, GE62TB0000025013100021</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>სხვა ხარჯები</t>
+  </si>
+  <si>
+    <t>GE62TB0000025013100021</t>
+  </si>
+  <si>
+    <t>დებიტორები - მისაღები ნაკრებების საკომისიო</t>
+  </si>
+  <si>
+    <t>TBCBGE22</t>
+  </si>
+  <si>
+    <t>ს.ს. თიბისი ბანკი</t>
+  </si>
+  <si>
+    <t>*SBC*</t>
+  </si>
+  <si>
     <t>საკურიერო მომსახურების, ონლაინ საკრედიტო ბარათებით გადახდილი თანხის გადარიცხვა.</t>
   </si>
   <si>
     <t>შპს აბრაჰამი, 405641836, TBCBGE22, GE55TB7714736020100006</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>შემოსავალი</t>
   </si>
   <si>
@@ -115,45 +139,111 @@
     <t>405641836</t>
   </si>
   <si>
-    <t>TBCBGE22</t>
-  </si>
-  <si>
     <t>სს "თიბისი ბანკი"</t>
   </si>
   <si>
+    <t>GMB</t>
+  </si>
+  <si>
+    <t>მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>დავითი საყვარელიძე, TBCBGE22, GE75TB7898145064300054</t>
+  </si>
+  <si>
+    <t>გადარიცხვა თანხის გატანა</t>
+  </si>
+  <si>
+    <t>GE75TB7898145064300054</t>
+  </si>
+  <si>
+    <t>დავითი საყვარელიძე</t>
+  </si>
+  <si>
+    <t>38001048993</t>
+  </si>
+  <si>
+    <t>406527600</t>
+  </si>
+  <si>
+    <t>შპს ცელერისი, 406527600</t>
+  </si>
+  <si>
     <t>GIB</t>
   </si>
   <si>
-    <t>ყვითელი ნაკრები ნაკრების საკომისიო, მაისი, 2026</t>
-  </si>
-  <si>
-    <t>დებიტორები - მისაღები ნაკრებების საკომისიო, TBCBGE22, GE62TB0000025013100021</t>
-  </si>
-  <si>
-    <t>სხვა ხარჯები</t>
-  </si>
-  <si>
-    <t>GE62TB0000025013100021</t>
-  </si>
-  <si>
-    <t>დებიტორები - მისაღები ნაკრებების საკომისიო</t>
-  </si>
-  <si>
-    <t>ს.ს. თიბისი ბანკი</t>
-  </si>
-  <si>
-    <t>*SBC*</t>
-  </si>
-  <si>
-    <t>მომსახურების ანაზღაურება</t>
+    <t>მიხეილ ლომჯარია, TBCBGE22, GE80TB7792445061600016</t>
+  </si>
+  <si>
+    <t>GE80TB7792445061600016</t>
+  </si>
+  <si>
+    <t>მიხეილ ლომჯარია</t>
+  </si>
+  <si>
+    <t>01010000461</t>
+  </si>
+  <si>
+    <t>ხელფასი</t>
+  </si>
+  <si>
+    <t>მარიამი გულბანი, TBCBGE22, GE73TB7072445064300053</t>
+  </si>
+  <si>
+    <t>GE73TB7072445064300053</t>
+  </si>
+  <si>
+    <t>მარიამი გულბანი</t>
+  </si>
+  <si>
+    <t>01911104191</t>
+  </si>
+  <si>
+    <t>გადასახადების ერთიანი კოდი</t>
+  </si>
+  <si>
+    <t>ხაზინის ერთიანი ანგარიში. საგადასახადო ინსპექცია (გადასახადები), TRESGE22, 101001000</t>
+  </si>
+  <si>
+    <t>საბიუჯეტო გადარიცხვები</t>
+  </si>
+  <si>
+    <t>101001000</t>
+  </si>
+  <si>
+    <t>ხაზინის ერთიანი ანგარიში. საგადასახადო ინსპექცია (გადასახადები)</t>
+  </si>
+  <si>
+    <t>TRESGE22</t>
+  </si>
+  <si>
+    <t>ფინანსთა სამინისტროს სახაზინო სამსახური</t>
+  </si>
+  <si>
+    <t>GIT</t>
+  </si>
+  <si>
+    <t>საშემოსავლო გადასახადი</t>
+  </si>
+  <si>
+    <t>საპენსიო დანამატი</t>
+  </si>
+  <si>
+    <t>სსიპ საქართველოს საპენსიო ფონდი, TBCBGE22, GE88TB7458336020100010</t>
+  </si>
+  <si>
+    <t>GE88TB7458336020100010</t>
+  </si>
+  <si>
+    <t>სსიპ საქართველოს საპენსიო ფონდი</t>
+  </si>
+  <si>
+    <t>205364407</t>
   </si>
   <si>
     <t>ბადრი სირაძე, TBCBGE22, GE67TB7692345061100079</t>
   </si>
   <si>
-    <t>გადარიცხვა თანხის გატანა</t>
-  </si>
-  <si>
     <t>GE67TB7692345061100079</t>
   </si>
   <si>
@@ -161,132 +251,6 @@
   </si>
   <si>
     <t>22001020425</t>
-  </si>
-  <si>
-    <t>406527600</t>
-  </si>
-  <si>
-    <t>შპს ცელერისი, 406527600</t>
-  </si>
-  <si>
-    <t>ელოიძე რობერტ, BAGAGE22, GE72BG0000000161067238</t>
-  </si>
-  <si>
-    <t>GE72BG0000000161067238</t>
-  </si>
-  <si>
-    <t>ელოიძე რობერტ</t>
-  </si>
-  <si>
-    <t>BAGAGE22</t>
-  </si>
-  <si>
-    <t>სს "საქართველოს ბანკი"</t>
-  </si>
-  <si>
-    <t>GIN</t>
-  </si>
-  <si>
-    <t>გადარიცხვის საკომისიო</t>
-  </si>
-  <si>
-    <t>საკომისიო შემოსავალი - იურიდიული პირების გარე გადარიცხვები, TBCBGE22, GE97TB0006001030220310</t>
-  </si>
-  <si>
-    <t>GE97TB0006001030220310</t>
-  </si>
-  <si>
-    <t>საკომისიო შემოსავალი - იურიდიული პირების გარე გადარიცხვები</t>
-  </si>
-  <si>
-    <t>მელაძე გიორგი, BAGAGE22, GE19BG0000000101042070</t>
-  </si>
-  <si>
-    <t>GE19BG0000000101042070</t>
-  </si>
-  <si>
-    <t>მელაძე გიორგი</t>
-  </si>
-  <si>
-    <t>დავით სვირავა, TBCBGE22, GE89TB7657745063600036</t>
-  </si>
-  <si>
-    <t>GE89TB7657745063600036</t>
-  </si>
-  <si>
-    <t>დავით სვირავა</t>
-  </si>
-  <si>
-    <t>62003016407</t>
-  </si>
-  <si>
-    <t>დავითი საყვარელიძე, TBCBGE22, GE75TB7898145064300054</t>
-  </si>
-  <si>
-    <t>GE75TB7898145064300054</t>
-  </si>
-  <si>
-    <t>დავითი საყვარელიძე</t>
-  </si>
-  <si>
-    <t>38001048993</t>
-  </si>
-  <si>
-    <t>ხელფასი</t>
-  </si>
-  <si>
-    <t>მარიამი გულბანი, TBCBGE22, GE73TB7072445064300053</t>
-  </si>
-  <si>
-    <t>GE73TB7072445064300053</t>
-  </si>
-  <si>
-    <t>მარიამი გულბანი</t>
-  </si>
-  <si>
-    <t>01911104191</t>
-  </si>
-  <si>
-    <t>გადასახადების ერთიანი კოდი</t>
-  </si>
-  <si>
-    <t>ხაზინის ერთიანი ანგარიში. საგადასახადო ინსპექცია (გადასახადები), TRESGE22, 101001000</t>
-  </si>
-  <si>
-    <t>საბიუჯეტო გადარიცხვები</t>
-  </si>
-  <si>
-    <t>101001000</t>
-  </si>
-  <si>
-    <t>ხაზინის ერთიანი ანგარიში. საგადასახადო ინსპექცია (გადასახადები)</t>
-  </si>
-  <si>
-    <t>TRESGE22</t>
-  </si>
-  <si>
-    <t>ფინანსთა სამინისტროს სახაზინო სამსახური</t>
-  </si>
-  <si>
-    <t>GIT</t>
-  </si>
-  <si>
-    <t>საშემოსავლო გადასახადი</t>
-  </si>
-  <si>
-    <t>საპენსიო დანამატი</t>
-  </si>
-  <si>
-    <t>სსიპ საქართველოს საპენსიო ფონდი, TBCBGE22, GE88TB7458336020100010</t>
-  </si>
-  <si>
-    <t>GE88TB7458336020100010</t>
-  </si>
-  <si>
-    <t>სსიპ საქართველოს საპენსიო ფონდი</t>
-  </si>
-  <si>
-    <t>205364407</t>
   </si>
 </sst>
 </file>
@@ -296,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -310,6 +274,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -336,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -347,6 +318,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,36 +600,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W16"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="72.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.81640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.7265625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="40.81640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="30.81640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="24.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="72.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="40.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="30.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.109375" style="2" customWidth="1"/>
     <col min="14" max="15" width="23" style="2" customWidth="1"/>
-    <col min="16" max="16" width="16.81640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.453125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="30.81640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="37.54296875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14.7265625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.453125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="24.7265625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="30.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="37.5546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="8.44140625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="24.6640625" style="2" customWidth="1"/>
     <col min="23" max="23" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.1796875" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="9.1796875" style="2"/>
+    <col min="24" max="24" width="9.109375" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,9 +700,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>46144</v>
+        <v>46206</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>23</v>
@@ -738,23 +710,23 @@
       <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="5">
-        <v>8000</v>
+      <c r="D2" s="5">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F2" s="5">
-        <v>10896.68</v>
+        <v>3387.76</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="4">
-        <v>46144</v>
+        <v>46206</v>
       </c>
       <c r="I2" s="2">
-        <v>1777713225</v>
+        <v>4297300</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>27</v>
@@ -763,73 +735,73 @@
         <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="T2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="W2" s="2">
+        <v>20321837945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="5">
+        <v>13387.76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46209</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1783326018</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="2">
-        <v>19575071489</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46145</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="5">
-        <v>10</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="5">
-        <v>10886.68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="4">
-        <v>46145</v>
-      </c>
-      <c r="I3" s="2">
-        <v>4107807</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="R3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="T3" s="2" t="s">
         <v>25</v>
       </c>
@@ -837,12 +809,12 @@
         <v>39</v>
       </c>
       <c r="W3" s="2">
-        <v>19582640453</v>
+        <v>20361908483</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>46146</v>
+        <v>46209</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>40</v>
@@ -851,22 +823,22 @@
         <v>41</v>
       </c>
       <c r="D4" s="5">
-        <v>1114</v>
+        <v>1204</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="5">
-        <v>9772.68</v>
+        <v>12183.76</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H4" s="4">
-        <v>46146</v>
+        <v>46209</v>
       </c>
       <c r="I4" s="2">
-        <v>1777879936</v>
+        <v>1783330310</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>43</v>
@@ -878,10 +850,10 @@
         <v>45</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>46</v>
@@ -893,54 +865,54 @@
         <v>25</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W4" s="2">
-        <v>19594083635</v>
+        <v>20365155941</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>46146</v>
+        <v>46209</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5">
-        <v>1368.47</v>
+        <v>320.37</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="5">
-        <v>8404.2099999999991</v>
+        <v>11863.39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H5" s="4">
-        <v>46146</v>
+        <v>46209</v>
       </c>
       <c r="I5" s="2">
-        <v>1777879956</v>
+        <v>1783330330</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>46</v>
@@ -952,107 +924,113 @@
         <v>25</v>
       </c>
       <c r="U5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="2">
+        <v>20365156235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="W5" s="2">
-        <v>19594083869</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46146</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="5">
+        <v>150</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5">
+        <v>11713.39</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46209</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1783330399</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="5">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="5">
-        <v>8399.2099999999991</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="4">
-        <v>46146</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1777879956</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="R6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="T6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W6" s="2">
+        <v>20365156273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>46216</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="W6" s="2">
-        <v>19594083870</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46146</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D7" s="5">
-        <v>1267.17</v>
+        <v>100</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="5">
-        <v>7132.04</v>
+        <v>11613.39</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H7" s="4">
-        <v>46146</v>
+        <v>46216</v>
       </c>
       <c r="I7" s="2">
-        <v>1777879978</v>
+        <v>1783929638</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>46</v>
@@ -1064,107 +1042,116 @@
         <v>25</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="W7" s="2">
-        <v>19594083893</v>
+        <v>20450335493</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>46146</v>
+        <v>46218</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="5">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="5">
-        <v>7127.04</v>
+        <v>11413.39</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H8" s="4">
-        <v>46146</v>
+        <v>46218</v>
       </c>
       <c r="I8" s="2">
-        <v>1777879978</v>
+        <v>1783943182</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="W8" s="2">
-        <v>19594083894</v>
+        <v>20479757054</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>46146</v>
+        <v>46218</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D9" s="5">
-        <v>1535.75</v>
+        <v>37</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="5">
-        <v>5591.29</v>
+        <v>11376.39</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H9" s="4">
-        <v>46146</v>
+        <v>46218</v>
       </c>
       <c r="I9" s="2">
-        <v>1777880009</v>
+        <v>1784110933</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>46</v>
@@ -1176,54 +1163,54 @@
         <v>25</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W9" s="2">
-        <v>19594083949</v>
+        <v>20479757098</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>46146</v>
+        <v>46223</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5">
-        <v>1326</v>
+        <v>150</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="5">
-        <v>4265.29</v>
+        <v>11226.39</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="4">
-        <v>46146</v>
+        <v>46223</v>
       </c>
       <c r="I10" s="2">
-        <v>1777880034</v>
+        <v>1784532326</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>46</v>
@@ -1235,54 +1222,54 @@
         <v>25</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W10" s="2">
-        <v>19594084173</v>
+        <v>20535001818</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>46146</v>
+        <v>46223</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5">
-        <v>300</v>
+        <v>539.71</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="5">
-        <v>3965.29</v>
+        <v>10686.68</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H11" s="4">
-        <v>46146</v>
+        <v>46223</v>
       </c>
       <c r="I11" s="2">
-        <v>1777880066</v>
+        <v>1784532391</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>46</v>
@@ -1294,54 +1281,54 @@
         <v>25</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W11" s="2">
-        <v>19594084265</v>
+        <v>20535001826</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>46153</v>
+        <v>46223</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="5">
-        <v>300</v>
+        <v>1368.31</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="5">
-        <v>3665.29</v>
+        <v>9318.3700000000008</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H12" s="4">
-        <v>46153</v>
+        <v>46223</v>
       </c>
       <c r="I12" s="2">
-        <v>1778484973</v>
+        <v>1784532438</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>46</v>
@@ -1353,54 +1340,54 @@
         <v>25</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W12" s="2">
-        <v>19681174909</v>
+        <v>20535001982</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46153</v>
+        <v>46230</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D13" s="5">
-        <v>1371</v>
+        <v>1536.33</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="5">
-        <v>2294.29</v>
+        <v>7782.04</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H13" s="4">
-        <v>46153</v>
+        <v>46230</v>
       </c>
       <c r="I13" s="2">
-        <v>1778485034</v>
+        <v>1785143005</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>46</v>
@@ -1412,54 +1399,54 @@
         <v>25</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W13" s="2">
-        <v>19681174935</v>
+        <v>20622761373</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>46155</v>
+        <v>46230</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="D14" s="5">
-        <v>285</v>
+        <v>1369.61</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="5">
-        <v>2009.29</v>
+        <v>6412.43</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="H14" s="4">
-        <v>46154</v>
+        <v>46230</v>
       </c>
       <c r="I14" s="2">
-        <v>1778587404</v>
+        <v>1785143045</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>46</v>
@@ -1468,60 +1455,57 @@
         <v>47</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="W14" s="2">
-        <v>19697969316</v>
+        <v>20622761501</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>46157</v>
+        <v>46230</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D15" s="5">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="5">
-        <v>1953.29</v>
+        <v>6032.43</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="4">
-        <v>46157</v>
+        <v>46230</v>
       </c>
       <c r="I15" s="2">
-        <v>1778839158</v>
+        <v>1785143070</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>46</v>
@@ -1533,54 +1517,54 @@
         <v>25</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W15" s="2">
-        <v>19731650451</v>
+        <v>20622761525</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>46160</v>
+        <v>46230</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D16" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="5">
-        <v>1653.29</v>
+        <v>5932.43</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H16" s="4">
-        <v>46160</v>
+        <v>46230</v>
       </c>
       <c r="I16" s="2">
-        <v>1779091525</v>
+        <v>1785143104</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>46</v>
@@ -1592,139 +1576,21 @@
         <v>25</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="W16" s="2">
-        <v>19761815012</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46167</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="5">
-        <v>833.69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5">
-        <v>819.6</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="4">
-        <v>46167</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1779694746</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W17" s="2">
-        <v>19843327980</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46167</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="5">
-        <v>100</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="5">
-        <v>719.6</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="4">
-        <v>46167</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1779694765</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W18" s="2">
-        <v>19843328020</v>
+        <v>20622761539</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z18" xr:uid="{00000000-0009-0000-0000-000001000000}">
+  <autoFilter ref="A1:Z16" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="ხელფასი"/>
+        <filter val="მომსახურების ანაზღაურება"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>